--- a/Pandas/exemple.xlsx
+++ b/Pandas/exemple.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Desktop\Cours\Master Cybersécurité\Projet service d'admission\Code projet\SA_Plateforme\Pandas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44281EC6-FB9F-4ED4-9EA2-7D4F5599CB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E44309-5B85-4BD6-A1FE-A07234D77F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2256,7 +2256,7 @@
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20" style="3" customWidth="1"/>
     <col min="5" max="5" width="7.85546875" customWidth="1"/>
     <col min="6" max="6" width="4.140625" customWidth="1"/>
     <col min="7" max="7" width="17.140625" customWidth="1"/>
